--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="47">
   <si>
     <t>_ID</t>
   </si>
@@ -180,6 +180,27 @@
     <t>道术加成</t>
   </si>
   <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>爆伤</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>物伤加成</t>
+  </si>
+  <si>
+    <t>法伤加成</t>
+  </si>
+  <si>
+    <t>道伤加成</t>
+  </si>
+  <si>
     <t>物攻倍率</t>
   </si>
   <si>
@@ -189,37 +210,31 @@
     <t>道术倍率</t>
   </si>
   <si>
-    <t>物伤加成</t>
-  </si>
-  <si>
-    <t>法伤加成</t>
-  </si>
-  <si>
-    <t>道伤加成</t>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>命中</t>
   </si>
   <si>
     <t>攻击倍率</t>
   </si>
   <si>
-    <t>防御倍率</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>减伤倍率</t>
-  </si>
-  <si>
-    <t>2,4,5,9,10</t>
-  </si>
-  <si>
-    <t>21,23</t>
-  </si>
-  <si>
-    <t>21,22,23,24,25,27,29,30</t>
-  </si>
-  <si>
-    <t>22,24,25,29,30</t>
+    <t>经验增幅</t>
+  </si>
+  <si>
+    <t>爆率增幅</t>
+  </si>
+  <si>
+    <t>金币增幅</t>
+  </si>
+  <si>
+    <t>品质增幅</t>
   </si>
 </sst>
 </file>
@@ -232,7 +247,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,6 +266,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -733,145 +754,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1553,7 +1573,7 @@
       <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="1">
@@ -1594,7 +1614,7 @@
       <c r="H12" s="1">
         <v>10</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J12" s="1">
@@ -1635,7 +1655,7 @@
       <c r="H13" s="1">
         <v>15</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J13" s="1">
@@ -1676,7 +1696,7 @@
       <c r="H14" s="1">
         <v>20</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J14" s="1">
@@ -1717,7 +1737,7 @@
       <c r="H15" s="1">
         <v>25</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J15" s="1">
@@ -1758,7 +1778,7 @@
       <c r="H16" s="1">
         <v>30</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="1">
@@ -1799,7 +1819,7 @@
       <c r="H17" s="1">
         <v>35</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J17" s="1">
@@ -1840,7 +1860,7 @@
       <c r="H18" s="1">
         <v>40</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J18" s="1">
@@ -1881,7 +1901,7 @@
       <c r="H19" s="1">
         <v>50</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="1">
@@ -1904,7 +1924,7 @@
       </c>
     </row>
     <row r="20" spans="9:9">
-      <c r="I20" s="3"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="3:15">
       <c r="C21" s="1">
@@ -1925,7 +1945,7 @@
       <c r="H21" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="1">
@@ -1966,7 +1986,7 @@
       <c r="H22" s="1">
         <v>10</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J22" s="1">
@@ -2007,7 +2027,7 @@
       <c r="H23" s="1">
         <v>15</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="1">
@@ -2048,7 +2068,7 @@
       <c r="H24" s="1">
         <v>20</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="1">
@@ -2089,7 +2109,7 @@
       <c r="H25" s="1">
         <v>25</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J25" s="1">
@@ -2130,7 +2150,7 @@
       <c r="H26" s="1">
         <v>30</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="1">
@@ -2171,7 +2191,7 @@
       <c r="H27" s="1">
         <v>35</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J27" s="1">
@@ -2212,7 +2232,7 @@
       <c r="H28" s="1">
         <v>40</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="1">
@@ -2253,7 +2273,7 @@
       <c r="H29" s="1">
         <v>50</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J29" s="1">
@@ -2276,7 +2296,7 @@
       </c>
     </row>
     <row r="30" spans="9:9">
-      <c r="I30" s="3"/>
+      <c r="I30" s="4"/>
     </row>
     <row r="31" spans="3:15">
       <c r="C31" s="1">
@@ -2297,7 +2317,7 @@
       <c r="H31" s="1">
         <v>5</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J31" s="1">
@@ -2338,7 +2358,7 @@
       <c r="H32" s="1">
         <v>10</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J32" s="1">
@@ -2379,7 +2399,7 @@
       <c r="H33" s="1">
         <v>15</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J33" s="1">
@@ -2420,7 +2440,7 @@
       <c r="H34" s="1">
         <v>20</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J34" s="1">
@@ -2461,7 +2481,7 @@
       <c r="H35" s="1">
         <v>25</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J35" s="1">
@@ -2502,7 +2522,7 @@
       <c r="H36" s="1">
         <v>30</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J36" s="1">
@@ -2543,7 +2563,7 @@
       <c r="H37" s="1">
         <v>35</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="1">
@@ -2584,7 +2604,7 @@
       <c r="H38" s="1">
         <v>40</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J38" s="1">
@@ -2625,7 +2645,7 @@
       <c r="H39" s="1">
         <v>5</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J39" s="1">
@@ -2666,7 +2686,7 @@
       <c r="H40" s="1">
         <v>10</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J40" s="1">
@@ -2707,7 +2727,7 @@
       <c r="H41" s="1">
         <v>15</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="1">
@@ -2748,7 +2768,7 @@
       <c r="H42" s="1">
         <v>20</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J42" s="1">
@@ -2789,7 +2809,7 @@
       <c r="H43" s="1">
         <v>25</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J43" s="1">
@@ -2830,7 +2850,7 @@
       <c r="H44" s="1">
         <v>30</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J44" s="1">
@@ -2871,7 +2891,7 @@
       <c r="H45" s="1">
         <v>35</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J45" s="1">
@@ -2912,7 +2932,7 @@
       <c r="H46" s="1">
         <v>40</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J46" s="1">
@@ -2953,7 +2973,7 @@
       <c r="H47" s="1">
         <v>50</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="1">
@@ -2994,7 +3014,7 @@
       <c r="H49" s="1">
         <v>3</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J49" s="1">
@@ -3006,10 +3026,10 @@
       <c r="L49" s="1">
         <v>1</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="4">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
+      <c r="N49" s="4">
         <v>6</v>
       </c>
       <c r="O49" s="1">
@@ -3035,7 +3055,7 @@
       <c r="H50" s="1">
         <v>4</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J50" s="1">
@@ -3047,10 +3067,10 @@
       <c r="L50" s="1">
         <v>1</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50" s="4">
         <v>4</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N50" s="4">
         <v>6</v>
       </c>
       <c r="O50" s="1">
@@ -3076,7 +3096,7 @@
       <c r="H51" s="1">
         <v>5</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J51" s="1">
@@ -3088,10 +3108,10 @@
       <c r="L51" s="1">
         <v>1</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M51" s="4">
         <v>4</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51" s="4">
         <v>6</v>
       </c>
       <c r="O51" s="1">
@@ -3117,7 +3137,7 @@
       <c r="H52" s="1">
         <v>5</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J52" s="1">
@@ -3129,10 +3149,10 @@
       <c r="L52" s="1">
         <v>1</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="4">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="4">
         <v>6</v>
       </c>
       <c r="O52" s="1">
@@ -3158,7 +3178,7 @@
       <c r="H53" s="1">
         <v>5</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="I53" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J53" s="1">
@@ -3170,10 +3190,10 @@
       <c r="L53" s="1">
         <v>1</v>
       </c>
-      <c r="M53" s="3">
+      <c r="M53" s="4">
         <v>4</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N53" s="4">
         <v>6</v>
       </c>
       <c r="O53" s="1">
@@ -3199,7 +3219,7 @@
       <c r="H54" s="1">
         <v>5</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J54" s="1">
@@ -3211,10 +3231,10 @@
       <c r="L54" s="1">
         <v>1</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="4">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="4">
         <v>6</v>
       </c>
       <c r="O54" s="1">
@@ -3222,7 +3242,7 @@
       </c>
     </row>
     <row r="55" spans="9:9">
-      <c r="I55" s="3"/>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="3:15">
       <c r="C56" s="1">
@@ -3243,7 +3263,7 @@
       <c r="H56" s="1">
         <v>3</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J56" s="1">
@@ -3255,10 +3275,10 @@
       <c r="L56" s="1">
         <v>1</v>
       </c>
-      <c r="M56" s="3">
+      <c r="M56" s="4">
         <v>4</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56" s="4">
         <v>6</v>
       </c>
       <c r="O56" s="1">
@@ -3284,7 +3304,7 @@
       <c r="H57" s="1">
         <v>4</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J57" s="1">
@@ -3296,10 +3316,10 @@
       <c r="L57" s="1">
         <v>1</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="4">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="4">
         <v>6</v>
       </c>
       <c r="O57" s="1">
@@ -3325,7 +3345,7 @@
       <c r="H58" s="1">
         <v>5</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J58" s="1">
@@ -3337,10 +3357,10 @@
       <c r="L58" s="1">
         <v>1</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="4">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="4">
         <v>6</v>
       </c>
       <c r="O58" s="1">
@@ -3366,7 +3386,7 @@
       <c r="H59" s="1">
         <v>5</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J59" s="1">
@@ -3378,10 +3398,10 @@
       <c r="L59" s="1">
         <v>1</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="4">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="4">
         <v>6</v>
       </c>
       <c r="O59" s="1">
@@ -3407,7 +3427,7 @@
       <c r="H60" s="1">
         <v>5</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="I60" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J60" s="1">
@@ -3419,10 +3439,10 @@
       <c r="L60" s="1">
         <v>1</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="4">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="4">
         <v>6</v>
       </c>
       <c r="O60" s="1">
@@ -3448,7 +3468,7 @@
       <c r="H61" s="1">
         <v>5</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="I61" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J61" s="1">
@@ -3460,10 +3480,10 @@
       <c r="L61" s="1">
         <v>1</v>
       </c>
-      <c r="M61" s="3">
+      <c r="M61" s="4">
         <v>4</v>
       </c>
-      <c r="N61" s="3">
+      <c r="N61" s="4">
         <v>6</v>
       </c>
       <c r="O61" s="1">
@@ -3489,7 +3509,7 @@
       <c r="H63" s="1">
         <v>3</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J63" s="1">
@@ -3501,10 +3521,10 @@
       <c r="L63" s="1">
         <v>1</v>
       </c>
-      <c r="M63" s="3">
+      <c r="M63" s="4">
         <v>4</v>
       </c>
-      <c r="N63" s="3">
+      <c r="N63" s="4">
         <v>6</v>
       </c>
       <c r="O63" s="1">
@@ -3530,7 +3550,7 @@
       <c r="H64" s="1">
         <v>4</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J64" s="1">
@@ -3542,10 +3562,10 @@
       <c r="L64" s="1">
         <v>1</v>
       </c>
-      <c r="M64" s="3">
+      <c r="M64" s="4">
         <v>4</v>
       </c>
-      <c r="N64" s="3">
+      <c r="N64" s="4">
         <v>6</v>
       </c>
       <c r="O64" s="1">
@@ -3571,7 +3591,7 @@
       <c r="H65" s="1">
         <v>5</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J65" s="1">
@@ -3583,10 +3603,10 @@
       <c r="L65" s="1">
         <v>1</v>
       </c>
-      <c r="M65" s="3">
+      <c r="M65" s="4">
         <v>4</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65" s="4">
         <v>6</v>
       </c>
       <c r="O65" s="1">
@@ -3612,7 +3632,7 @@
       <c r="H66" s="1">
         <v>5</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I66" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J66" s="1">
@@ -3624,10 +3644,10 @@
       <c r="L66" s="1">
         <v>1</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="4">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="4">
         <v>6</v>
       </c>
       <c r="O66" s="1">
@@ -3653,7 +3673,7 @@
       <c r="H67" s="1">
         <v>5</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J67" s="1">
@@ -3665,10 +3685,10 @@
       <c r="L67" s="1">
         <v>1</v>
       </c>
-      <c r="M67" s="3">
+      <c r="M67" s="4">
         <v>4</v>
       </c>
-      <c r="N67" s="3">
+      <c r="N67" s="4">
         <v>6</v>
       </c>
       <c r="O67" s="1">
@@ -3694,7 +3714,7 @@
       <c r="H68" s="1">
         <v>5</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J68" s="1">
@@ -3706,10 +3726,10 @@
       <c r="L68" s="1">
         <v>1</v>
       </c>
-      <c r="M68" s="3">
+      <c r="M68" s="4">
         <v>4</v>
       </c>
-      <c r="N68" s="3">
+      <c r="N68" s="4">
         <v>6</v>
       </c>
       <c r="O68" s="1">
@@ -3733,22 +3753,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:O32"/>
+  <dimension ref="C3:I55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="8.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16" width="19.25" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:15">
+    <row r="3" s="1" customFormat="1" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -3756,40 +3773,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="4" s="1" customFormat="1" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
@@ -3797,40 +3796,22 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="5" s="1" customFormat="1" spans="3:9">
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
@@ -3838,10 +3819,10 @@
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -3850,1102 +3831,565 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:9">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>7</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:9">
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3">
         <v>8</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1">
-        <v>750</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L6" s="1">
-        <v>6</v>
-      </c>
-      <c r="M6" s="1">
-        <v>6</v>
-      </c>
-      <c r="N6" s="1">
-        <v>6</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:15">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2004</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="1">
-        <v>750</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L7" s="1">
-        <v>6</v>
-      </c>
-      <c r="M7" s="1">
-        <v>6</v>
-      </c>
-      <c r="N7" s="3">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:9">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>2005</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="1">
-        <v>750</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L8" s="1">
-        <v>6</v>
-      </c>
-      <c r="M8" s="1">
-        <v>6</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1</v>
-      </c>
-      <c r="O8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:9">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>2006</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H9" s="1">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="1">
-        <v>750</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L9" s="1">
-        <v>6</v>
-      </c>
-      <c r="M9" s="1">
-        <v>6</v>
-      </c>
-      <c r="N9" s="3">
-        <v>1</v>
-      </c>
-      <c r="O9" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="3:15">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="3:9">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9">
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1">
         <v>33</v>
       </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="1">
-        <v>5</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="E11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="1">
-        <v>750</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L10" s="1">
-        <v>6</v>
-      </c>
-      <c r="M10" s="1">
-        <v>6</v>
-      </c>
-      <c r="N10" s="3">
-        <v>2</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="3:15">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>34</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="1">
-        <v>5</v>
-      </c>
       <c r="H11" s="1">
-        <v>10</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="1">
-        <v>750</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L11" s="1">
-        <v>6</v>
-      </c>
-      <c r="M11" s="1">
-        <v>6</v>
-      </c>
-      <c r="N11" s="3">
-        <v>2</v>
-      </c>
-      <c r="O11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="3:15">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:9">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
+        <v>34</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="3:9">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
         <v>35</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="1">
-        <v>5</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
         <v>10</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="1">
-        <v>750</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L12" s="1">
-        <v>6</v>
-      </c>
-      <c r="M12" s="1">
-        <v>6</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2</v>
-      </c>
-      <c r="O12" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="3:15">
-      <c r="C13" s="1">
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:9">
+      <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D13" s="1">
-        <v>2001</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>3</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="1">
-        <v>750</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L13" s="1">
-        <v>6</v>
-      </c>
-      <c r="M13" s="1">
-        <v>6</v>
-      </c>
-      <c r="N13" s="3">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="3:15">
-      <c r="C14" s="1">
+      <c r="D14" s="1">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
         <v>10</v>
-      </c>
-      <c r="D14" s="1">
-        <v>2002</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="1">
-        <v>750</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L14" s="1">
-        <v>6</v>
-      </c>
-      <c r="M14" s="1">
-        <v>6</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="3:15">
+      <c r="I14" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:9">
       <c r="C15" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1">
-        <v>2003</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H15" s="1">
         <v>3</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="1">
-        <v>750</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L15" s="1">
-        <v>6</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1</v>
-      </c>
-      <c r="O15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="3:15">
+      <c r="I15" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="3:9">
       <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="3:9">
+      <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D16" s="1">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="1">
-        <v>25</v>
-      </c>
-      <c r="H16" s="1">
-        <v>50</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="1">
-        <v>750</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L16" s="1">
-        <v>6</v>
-      </c>
-      <c r="M16" s="1">
-        <v>6</v>
-      </c>
-      <c r="N16" s="1">
-        <v>6</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:15">
-      <c r="C17" s="1">
+      <c r="D17" s="1">
+        <v>24</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="3:9">
+      <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D17" s="1">
-        <v>19</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="1">
-        <v>25</v>
-      </c>
-      <c r="H17" s="1">
-        <v>50</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="1">
-        <v>750</v>
-      </c>
-      <c r="K17" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L17" s="1">
-        <v>6</v>
-      </c>
-      <c r="M17" s="1">
-        <v>6</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="3:15">
-      <c r="C18" s="1">
+      <c r="D18" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4</v>
+      </c>
+      <c r="I18" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="3:9">
+      <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D18" s="1">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="1">
-        <v>25</v>
-      </c>
-      <c r="H18" s="1">
-        <v>50</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="1">
-        <v>750</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L18" s="1">
-        <v>6</v>
-      </c>
-      <c r="M18" s="1">
-        <v>6</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6</v>
-      </c>
-      <c r="O18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="3:15">
-      <c r="C19" s="1">
+      <c r="D19" s="1">
+        <v>2005</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+      <c r="I19" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="3:9">
+      <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D19" s="1">
-        <v>24</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="1">
-        <v>25</v>
-      </c>
-      <c r="H19" s="1">
-        <v>50</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="1">
-        <v>750</v>
-      </c>
-      <c r="K19" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L19" s="1">
-        <v>6</v>
-      </c>
-      <c r="M19" s="1">
-        <v>6</v>
-      </c>
-      <c r="N19" s="1">
-        <v>6</v>
-      </c>
-      <c r="O19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="3:15">
-      <c r="C20" s="1">
+      <c r="D20" s="1">
+        <v>2006</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4</v>
+      </c>
+      <c r="I20" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="3:9">
+      <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D20" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="D21" s="1">
+        <v>2002</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J20" s="1">
-        <v>750</v>
-      </c>
-      <c r="K20" s="1">
-        <v>1050</v>
-      </c>
-      <c r="L20" s="1">
-        <v>6</v>
-      </c>
-      <c r="M20" s="1">
-        <v>6</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="9:15">
-      <c r="I21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="3:15">
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="3:9">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1">
+        <v>2003</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
         <v>7</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="1">
-        <v>20</v>
-      </c>
-      <c r="H22" s="1">
-        <v>50</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L22" s="1">
-        <v>7</v>
-      </c>
-      <c r="M22" s="1">
-        <v>7</v>
-      </c>
-      <c r="N22" s="1">
-        <v>6</v>
-      </c>
-      <c r="O22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="23" s="1" customFormat="1" spans="3:9">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1">
-        <v>2004</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H23" s="1">
-        <v>10</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L23" s="1">
+        <v>6</v>
+      </c>
+      <c r="I23" s="1">
         <v>7</v>
       </c>
-      <c r="M23" s="1">
-        <v>7</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2</v>
-      </c>
-      <c r="O23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="24" s="1" customFormat="1" spans="3:9">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1">
-        <v>2005</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H24" s="1">
-        <v>10</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L24" s="1">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1">
         <v>7</v>
       </c>
-      <c r="M24" s="1">
-        <v>7</v>
-      </c>
-      <c r="N24" s="3">
-        <v>2</v>
-      </c>
-      <c r="O24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="25" s="1" customFormat="1" spans="3:9">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
-        <v>2006</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>30</v>
+        <v>2001</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H25" s="1">
+        <v>6</v>
+      </c>
+      <c r="I25" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="3:9">
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
         <v>10</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K25" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="H26" s="1">
         <v>7</v>
       </c>
-      <c r="M25" s="1">
+      <c r="I26" s="1">
         <v>7</v>
       </c>
-      <c r="N25" s="3">
-        <v>2</v>
-      </c>
-      <c r="O25" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="3:15">
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1">
-        <v>33</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="1">
-        <v>20</v>
-      </c>
-      <c r="H26" s="1">
-        <v>40</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L26" s="1">
-        <v>7</v>
-      </c>
-      <c r="M26" s="1">
-        <v>7</v>
-      </c>
-      <c r="N26" s="3">
-        <v>3</v>
-      </c>
-      <c r="O26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="27" s="1" customFormat="1" spans="3:9">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1">
-        <v>34</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
       </c>
       <c r="G27" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H27" s="1">
-        <v>40</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L27" s="1">
         <v>7</v>
       </c>
-      <c r="M27" s="1">
+      <c r="I27" s="1">
         <v>7</v>
       </c>
-      <c r="N27" s="3">
-        <v>3</v>
-      </c>
-      <c r="O27" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="28" s="1" customFormat="1" spans="3:9">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1">
-        <v>35</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H28" s="1">
-        <v>40</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L28" s="1">
         <v>7</v>
       </c>
-      <c r="M28" s="1">
+      <c r="I28" s="1">
         <v>7</v>
       </c>
-      <c r="N28" s="3">
-        <v>3</v>
-      </c>
-      <c r="O28" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="3:15">
+    </row>
+    <row r="29" s="1" customFormat="1" spans="3:9">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1">
-        <v>2001</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H29" s="1">
-        <v>10</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L29" s="1">
         <v>7</v>
       </c>
-      <c r="M29" s="1">
+      <c r="I29" s="1">
         <v>7</v>
       </c>
-      <c r="N29" s="3">
-        <v>1</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="3:15">
-      <c r="C30" s="1">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2002</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="1">
-        <v>5</v>
-      </c>
-      <c r="H30" s="1">
-        <v>10</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L30" s="1">
-        <v>7</v>
-      </c>
-      <c r="M30" s="1">
-        <v>7</v>
-      </c>
-      <c r="N30" s="3">
-        <v>3</v>
-      </c>
-      <c r="O30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="3:15">
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2003</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="1">
-        <v>5</v>
-      </c>
-      <c r="H31" s="1">
-        <v>10</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K31" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L31" s="1">
-        <v>7</v>
-      </c>
-      <c r="M31" s="1">
-        <v>7</v>
-      </c>
-      <c r="N31" s="3">
-        <v>3</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="3:15">
-      <c r="C32" s="1">
-        <v>31</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="1">
-        <v>5</v>
-      </c>
-      <c r="H32" s="1">
-        <v>10</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1100</v>
-      </c>
-      <c r="K32" s="1">
-        <v>1100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32" s="1">
-        <v>7</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="81" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1622,7 +1622,7 @@
         <v>31</v>
       </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F23" s="1">
         <v>6</v>
@@ -1645,7 +1645,7 @@
         <v>32</v>
       </c>
       <c r="E24" s="1">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F24" s="1">
         <v>6</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="宠物" sheetId="2" r:id="rId1"/>
@@ -1144,7 +1144,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:I55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
@@ -1154,7 +1154,7 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:9">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:9">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:9">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:9">
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:9">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:9">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1277,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -1369,7 +1369,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F12" s="1">
         <v>2</v>
@@ -1392,7 +1392,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
@@ -1415,7 +1415,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -1484,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -1507,7 +1507,7 @@
         <v>2004</v>
       </c>
       <c r="E18" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -1530,7 +1530,7 @@
         <v>2005</v>
       </c>
       <c r="E19" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -1553,7 +1553,7 @@
         <v>2006</v>
       </c>
       <c r="E20" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -1576,7 +1576,7 @@
         <v>2002</v>
       </c>
       <c r="E21" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -1599,7 +1599,7 @@
         <v>2003</v>
       </c>
       <c r="E22" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
@@ -1668,7 +1668,7 @@
         <v>2001</v>
       </c>
       <c r="E25" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1">
         <v>6</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1277,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -1369,7 +1369,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F12" s="1">
         <v>2</v>
@@ -1392,7 +1392,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
@@ -1415,7 +1415,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="1">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="1">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1">
         <v>3</v>
@@ -1484,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -1507,7 +1507,7 @@
         <v>2004</v>
       </c>
       <c r="E18" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -1530,7 +1530,7 @@
         <v>2005</v>
       </c>
       <c r="E19" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -1553,7 +1553,7 @@
         <v>2006</v>
       </c>
       <c r="E20" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -1576,7 +1576,7 @@
         <v>2002</v>
       </c>
       <c r="E21" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -1668,7 +1668,7 @@
         <v>2001</v>
       </c>
       <c r="E25" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1">
         <v>6</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1231,7 +1231,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1277,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -1323,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="E10" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1346,7 +1346,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -1369,7 +1369,7 @@
         <v>34</v>
       </c>
       <c r="E12" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1">
         <v>2</v>
@@ -1392,7 +1392,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F13" s="1">
         <v>2</v>
@@ -1507,7 +1507,7 @@
         <v>2004</v>
       </c>
       <c r="E18" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -1530,7 +1530,7 @@
         <v>2005</v>
       </c>
       <c r="E19" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -1553,7 +1553,7 @@
         <v>2006</v>
       </c>
       <c r="E20" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -1576,7 +1576,7 @@
         <v>2002</v>
       </c>
       <c r="E21" s="1">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -1599,7 +1599,7 @@
         <v>2003</v>
       </c>
       <c r="E22" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1277,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="E8" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -1484,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1">
         <v>3</v>
@@ -1507,7 +1507,7 @@
         <v>2004</v>
       </c>
       <c r="E18" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -1530,7 +1530,7 @@
         <v>2005</v>
       </c>
       <c r="E19" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -1553,7 +1553,7 @@
         <v>2006</v>
       </c>
       <c r="E20" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -1576,7 +1576,7 @@
         <v>2002</v>
       </c>
       <c r="E21" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -1599,7 +1599,7 @@
         <v>2003</v>
       </c>
       <c r="E22" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
@@ -1622,7 +1622,7 @@
         <v>31</v>
       </c>
       <c r="E23" s="1">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F23" s="1">
         <v>6</v>
@@ -1668,7 +1668,7 @@
         <v>2001</v>
       </c>
       <c r="E25" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F25" s="1">
         <v>6</v>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -161,10 +161,10 @@
     <t>经验增幅</t>
   </si>
   <si>
+    <t>金币增幅</t>
+  </si>
+  <si>
     <t>爆率增幅</t>
-  </si>
-  <si>
-    <t>金币增幅</t>
   </si>
   <si>
     <t>品质增幅</t>

--- a/Excel/PetConfig.xlsx
+++ b/Excel/PetConfig.xlsx
@@ -60,11 +60,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t>_ID</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>AttrId</t>
   </si>
   <si>
@@ -168,6 +171,30 @@
   </si>
   <si>
     <t>品质增幅</t>
+  </si>
+  <si>
+    <t>法攻倍率</t>
+  </si>
+  <si>
+    <t>道攻倍率</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>增伤倍率</t>
   </si>
 </sst>
 </file>
@@ -1143,18 +1170,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I55"/>
+  <dimension ref="C3:J59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:9">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1176,10 +1203,13 @@
       <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:9">
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="3:10">
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1197,588 +1227,1004 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:9">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="3:10">
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:9">
+        <v>10</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
         <v>7</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>50</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
       <c r="G6" s="1">
         <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:9">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
         <v>8</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>20</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
         <v>9</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>150</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
       <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:9">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
         <v>12</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>40</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="3:9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
         <v>13</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>30</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
       <c r="G10" s="1">
         <v>1</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="3:9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
         <v>33</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>50</v>
       </c>
-      <c r="F11" s="1">
-        <v>2</v>
-      </c>
       <c r="G11" s="1">
         <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="3:9">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
         <v>34</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>50</v>
       </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
       <c r="G12" s="1">
         <v>2</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="3:9">
+      <c r="I12" s="1">
+        <v>2</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
         <v>35</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>50</v>
       </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
       <c r="G13" s="1">
         <v>2</v>
       </c>
       <c r="H13" s="1">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
         <v>3</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="3:9">
+      <c r="J13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
         <v>18</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>100</v>
-      </c>
-      <c r="F14" s="1">
-        <v>3</v>
       </c>
       <c r="G14" s="1">
         <v>3</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="3:9">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="3:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
         <v>19</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>50</v>
-      </c>
-      <c r="F15" s="1">
-        <v>3</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="3:9">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="3:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
         <v>20</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>100</v>
-      </c>
-      <c r="F16" s="1">
-        <v>3</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="3:9">
+        <v>3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
         <v>24</v>
       </c>
-      <c r="E17" s="1">
+      <c r="F17" s="1">
         <v>50</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="3:9">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
         <v>2004</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>8</v>
-      </c>
-      <c r="F18" s="1">
-        <v>4</v>
       </c>
       <c r="G18" s="1">
         <v>4</v>
       </c>
       <c r="H18" s="1">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="3:9">
+        <v>4</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
         <v>2005</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>8</v>
-      </c>
-      <c r="F19" s="1">
-        <v>4</v>
       </c>
       <c r="G19" s="1">
         <v>4</v>
       </c>
       <c r="H19" s="1">
-        <v>2</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="3:9">
+        <v>4</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
         <v>2006</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>8</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4</v>
       </c>
       <c r="G20" s="1">
         <v>4</v>
       </c>
       <c r="H20" s="1">
+        <v>4</v>
+      </c>
+      <c r="I20" s="1">
         <v>3</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="3:9">
+      <c r="J20" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
         <v>2002</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>40</v>
-      </c>
-      <c r="F21" s="1">
-        <v>5</v>
       </c>
       <c r="G21" s="1">
         <v>5</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="3:9">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="3:10">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
         <v>2003</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>20</v>
-      </c>
-      <c r="F22" s="1">
-        <v>5</v>
       </c>
       <c r="G22" s="1">
         <v>5</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="3:9">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
         <v>31</v>
       </c>
-      <c r="E23" s="1">
+      <c r="F23" s="1">
         <v>0.4</v>
-      </c>
-      <c r="F23" s="1">
-        <v>6</v>
       </c>
       <c r="G23" s="1">
         <v>6</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="3:9">
+        <v>6</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="3:10">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
         <v>32</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>0.2</v>
-      </c>
-      <c r="F24" s="1">
-        <v>6</v>
       </c>
       <c r="G24" s="1">
         <v>6</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="3:9">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="3:10">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
         <v>2001</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>5</v>
-      </c>
-      <c r="F25" s="1">
-        <v>6</v>
       </c>
       <c r="G25" s="1">
         <v>6</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="3:9">
+        <v>6</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="3:10">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
         <v>50</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>0.1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>7</v>
       </c>
       <c r="G26" s="1">
         <v>7</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="3:9">
+        <v>7</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="3:10">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
         <v>51</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>0.1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>7</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="3:9">
+        <v>7</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="3:10">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
         <v>52</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>0.1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>7</v>
       </c>
       <c r="G28" s="1">
         <v>7</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="3:9">
+        <v>7</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="3:10">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
         <v>53</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>0.1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>7</v>
       </c>
       <c r="G29" s="1">
         <v>7</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10">
+      <c r="C32" s="1">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2003</v>
+      </c>
+      <c r="F32" s="1">
+        <v>20</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10">
+      <c r="C33" s="1">
+        <v>31</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F33" s="1">
+        <v>8</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10">
+      <c r="C34" s="1">
+        <v>32</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2005</v>
+      </c>
+      <c r="F34" s="1">
+        <v>8</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
+        <v>2</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10">
+      <c r="C35" s="1">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2006</v>
+      </c>
+      <c r="F35" s="1">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="1">
+        <v>3</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10">
+      <c r="C36" s="1">
+        <v>34</v>
+      </c>
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F36" s="1">
+        <v>8</v>
+      </c>
+      <c r="G36" s="1">
+        <v>3</v>
+      </c>
+      <c r="H36" s="1">
+        <v>3</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10">
+      <c r="C37" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="81" customHeight="1"/>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2008</v>
+      </c>
+      <c r="F37" s="1">
+        <v>8</v>
+      </c>
+      <c r="G37" s="1">
+        <v>3</v>
+      </c>
+      <c r="H37" s="1">
+        <v>3</v>
+      </c>
+      <c r="I37" s="1">
+        <v>2</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="3:10">
+      <c r="C38" s="1">
+        <v>36</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2009</v>
+      </c>
+      <c r="F38" s="1">
+        <v>8</v>
+      </c>
+      <c r="G38" s="1">
+        <v>3</v>
+      </c>
+      <c r="H38" s="1">
+        <v>3</v>
+      </c>
+      <c r="I38" s="1">
+        <v>3</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10">
+      <c r="C39" s="1">
+        <v>37</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2012</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10">
+      <c r="C40" s="1">
+        <v>38</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2001</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>5</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10">
+      <c r="C41" s="1">
+        <v>39</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="1">
+        <v>31</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G41" s="1">
+        <v>6</v>
+      </c>
+      <c r="H41" s="1">
+        <v>6</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10">
+      <c r="C42" s="1">
+        <v>40</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2013</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="1">
+        <v>7</v>
+      </c>
+      <c r="H42" s="1">
+        <v>7</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10">
+      <c r="C43" s="1">
+        <v>41</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>32</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G43" s="1">
+        <v>8</v>
+      </c>
+      <c r="H43" s="1">
+        <v>8</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10">
+      <c r="C44" s="1">
+        <v>42</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2010</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1">
+        <v>9</v>
+      </c>
+      <c r="H44" s="1">
+        <v>9</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="81" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3:I5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5 E3:E5 J3:J5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
